--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_9_14.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_9_14.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>159659.5749574617</v>
+        <v>170909.6219863851</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10172022.8537143</v>
+        <v>9865703.132607052</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22030310.40483281</v>
+        <v>22079133.17442485</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4013148.670637969</v>
+        <v>4012766.669217131</v>
       </c>
     </row>
     <row r="11">
@@ -8196,25 +8196,25 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>207.816926421865</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L5" t="n">
-        <v>220.5407667287812</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M5" t="n">
-        <v>213.4047658905893</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>212.1974656066412</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O5" t="n">
-        <v>213.8420104166616</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P5" t="n">
-        <v>217.3587042979831</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q5" t="n">
-        <v>211.8866747990726</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R5" t="n">
         <v>65.71641987298243</v>
@@ -8272,28 +8272,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J6" t="n">
-        <v>121.9604191194969</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>129.5055144460571</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>127.3457005345912</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>129.0540339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N6" t="n">
-        <v>117.915523404088</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>130.3139048218029</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>124.1167470369718</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q6" t="n">
-        <v>133.3921891803611</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8357,19 +8357,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>128.4503156255006</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M7" t="n">
-        <v>132.1416528000641</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N7" t="n">
-        <v>121.062724793102</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O7" t="n">
-        <v>132.3392925502035</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P7" t="n">
-        <v>132.4936433934099</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q7" t="n">
         <v>65.34295837775146</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>168.7626683457818</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>201.6804641103072</v>
+        <v>208.3214547517356</v>
       </c>
       <c r="L8" t="n">
-        <v>212.9279426081782</v>
+        <v>221.1666787354324</v>
       </c>
       <c r="M8" t="n">
-        <v>204.9340322222476</v>
+        <v>214.1012135983212</v>
       </c>
       <c r="N8" t="n">
-        <v>203.5896666116663</v>
+        <v>212.9051825663978</v>
       </c>
       <c r="O8" t="n">
-        <v>205.713909914149</v>
+        <v>214.5102874732696</v>
       </c>
       <c r="P8" t="n">
-        <v>210.4215585693399</v>
+        <v>217.9290633046618</v>
       </c>
       <c r="Q8" t="n">
-        <v>206.6771672613842</v>
+        <v>212.3149906599047</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>119.521815345912</v>
+        <v>122.1609165114202</v>
       </c>
       <c r="K9" t="n">
-        <v>125.3375521819062</v>
+        <v>129.8481964236088</v>
       </c>
       <c r="L9" t="n">
-        <v>121.7413609119497</v>
+        <v>127.8064787429921</v>
       </c>
       <c r="M9" t="n">
-        <v>122.5140339220183</v>
+        <v>129.5917403577182</v>
       </c>
       <c r="N9" t="n">
-        <v>111.2024290644654</v>
+        <v>118.4674613291454</v>
       </c>
       <c r="O9" t="n">
-        <v>124.1727350104822</v>
+        <v>130.8188201934042</v>
       </c>
       <c r="P9" t="n">
-        <v>119.1879168482925</v>
+        <v>124.5219861368073</v>
       </c>
       <c r="Q9" t="n">
-        <v>130.097396727531</v>
+        <v>133.663080786811</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,19 +8594,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>125.2331352976317</v>
+        <v>128.7148261097669</v>
       </c>
       <c r="M10" t="n">
-        <v>128.7495872262936</v>
+        <v>132.4205420186164</v>
       </c>
       <c r="N10" t="n">
-        <v>117.7513149570365</v>
+        <v>121.3349826493852</v>
       </c>
       <c r="O10" t="n">
-        <v>129.2806695993838</v>
+        <v>132.590766746692</v>
       </c>
       <c r="P10" t="n">
-        <v>129.8764630655411</v>
+        <v>132.7088230120157</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K11" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L11" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M11" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N11" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O11" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P11" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K12" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L13" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M13" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N13" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O13" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P13" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639999</v>
       </c>
       <c r="K14" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L14" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M14" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N14" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O14" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P14" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q14" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K15" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q15" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L16" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M16" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N16" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O16" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P16" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K17" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L17" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M17" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N17" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O17" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P17" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q17" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K18" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q18" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L19" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M19" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N19" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O19" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P19" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K20" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L20" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M20" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N20" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O20" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P20" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q20" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K21" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L22" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M22" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N22" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O22" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P22" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K23" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L23" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M23" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N23" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O23" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P23" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q23" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K24" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L25" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M25" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N25" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O25" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P25" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K26" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L26" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M26" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N26" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O26" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P26" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q26" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K27" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q27" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L28" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M28" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N28" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O28" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P28" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K29" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L29" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M29" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N29" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O29" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P29" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q29" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K30" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q30" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L31" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M31" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N31" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O31" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P31" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K32" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L32" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M32" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N32" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O32" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P32" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K33" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q33" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L34" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M34" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N34" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O34" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P34" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K35" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L35" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M35" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N35" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O35" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P35" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q35" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K36" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q36" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L37" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M37" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N37" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O37" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P37" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K38" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L38" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M38" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N38" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O38" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P38" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q38" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K39" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q39" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L40" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M40" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N40" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O40" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P40" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K41" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L41" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M41" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N41" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O41" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P41" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q41" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K42" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q42" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L43" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M43" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N43" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O43" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P43" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>79.70920603422395</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K44" t="n">
-        <v>68.21240883392525</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L44" t="n">
-        <v>47.3490179850626</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M44" t="n">
-        <v>20.69557493581544</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N44" t="n">
-        <v>16.37003847096275</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O44" t="n">
-        <v>28.9277239845008</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P44" t="n">
-        <v>59.53863897134994</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q44" t="n">
-        <v>93.37037831666055</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>66.48218327044026</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K45" t="n">
-        <v>34.68437293662313</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>11.9858602445189</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q45" t="n">
-        <v>58.43566087847434</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>66.78932374430589</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L46" t="n">
-        <v>55.25946316648418</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M46" t="n">
-        <v>54.97216099678541</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N46" t="n">
-        <v>45.72815102261019</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O46" t="n">
-        <v>62.75562041905589</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P46" t="n">
-        <v>72.95279093439355</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22756,16 +22756,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>415.2062551030747</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>338.4867016132546</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>206.7562513794511</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>3.760465234009502</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22786,19 +22786,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>143.8084546245668</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>206.8214766214212</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>222.6734978053374</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>251.3379343148717</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,16 +22835,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>137.2918945217012</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>111.7368781987606</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>87.61927436084903</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22868,16 +22868,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>96.95270207717144</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>170.7243031793095</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>199.9566532231235</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9379858545597</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,19 +22914,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.9477006699342</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H7" t="n">
-        <v>161.8423856221937</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>154.148966730537</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J7" t="n">
-        <v>90.29937683798425</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>17.24129510457138</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22941,22 +22941,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>82.53804325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>175.3474241640547</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
-        <v>223.2623685287755</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T7" t="n">
-        <v>227.7606713954946</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U7" t="n">
-        <v>286.3166687007532</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.1580138970446</v>
+        <v>415.2102214038314</v>
       </c>
       <c r="H8" t="n">
-        <v>337.9926513619983</v>
+        <v>338.5273214908784</v>
       </c>
       <c r="I8" t="n">
-        <v>204.8964322839738</v>
+        <v>206.909162189371</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.097100052852173</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23026,16 +23026,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>140.7781229662753</v>
+        <v>144.0576027644702</v>
       </c>
       <c r="S8" t="n">
-        <v>205.7221801390092</v>
+        <v>206.9118586999128</v>
       </c>
       <c r="T8" t="n">
-        <v>222.4623219259404</v>
+        <v>222.6908602868995</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3340750183893</v>
+        <v>251.3382516189322</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,13 +23072,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.2660832009465</v>
+        <v>137.2940166796957</v>
       </c>
       <c r="H9" t="n">
-        <v>111.4875951798927</v>
+        <v>111.757373777286</v>
       </c>
       <c r="I9" t="n">
-        <v>86.73059511556602</v>
+        <v>87.69233988828964</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>95.35013603943558</v>
+        <v>97.08446202703757</v>
       </c>
       <c r="S9" t="n">
-        <v>170.2448692170454</v>
+        <v>170.7637213332854</v>
       </c>
       <c r="T9" t="n">
-        <v>199.8526154872744</v>
+        <v>199.9652070090748</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9362877413522</v>
+        <v>225.9381254702172</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9260613256719</v>
+        <v>167.9494798159088</v>
       </c>
       <c r="H10" t="n">
-        <v>161.6499921795707</v>
+        <v>161.8582038473137</v>
       </c>
       <c r="I10" t="n">
-        <v>153.4982126321763</v>
+        <v>154.2024705022108</v>
       </c>
       <c r="J10" t="n">
-        <v>88.76947519864</v>
+        <v>90.42516245839145</v>
       </c>
       <c r="K10" t="n">
-        <v>14.72719674391564</v>
+        <v>17.44799951871617</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>80.72604325169439</v>
+        <v>82.6870224659892</v>
       </c>
       <c r="R10" t="n">
-        <v>174.3744405574974</v>
+        <v>175.4274210366964</v>
       </c>
       <c r="S10" t="n">
-        <v>222.8852537746772</v>
+        <v>223.2933741908973</v>
       </c>
       <c r="T10" t="n">
-        <v>227.6682123791012</v>
+        <v>227.7682732010226</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3154883728843</v>
+        <v>286.3167657450791</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H11" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I11" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S11" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T11" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H12" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I12" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S12" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T12" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U12" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H13" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I13" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J13" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R13" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S13" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T13" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H14" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I14" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S14" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T14" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H15" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I15" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618534</v>
       </c>
       <c r="S15" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T15" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U15" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H16" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I16" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J16" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611378</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046782</v>
       </c>
       <c r="R16" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S16" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T16" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H17" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I17" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S17" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T17" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H18" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I18" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S18" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T18" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U18" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H19" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I19" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J19" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R19" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S19" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T19" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H20" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I20" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S20" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T20" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H21" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I21" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S21" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T21" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U21" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H22" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I22" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J22" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R22" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S22" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T22" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H23" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I23" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S23" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T23" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H24" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I24" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S24" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T24" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U24" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H25" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I25" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J25" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R25" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S25" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T25" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H26" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I26" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S26" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T26" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H27" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I27" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S27" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T27" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U27" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H28" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I28" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J28" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R28" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S28" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T28" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H29" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I29" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S29" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T29" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H30" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I30" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S30" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T30" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U30" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H31" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I31" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J31" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R31" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S31" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T31" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H32" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I32" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S32" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T32" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H33" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I33" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S33" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T33" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U33" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H34" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I34" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J34" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R34" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S34" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T34" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H35" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I35" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S35" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T35" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H36" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I36" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S36" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T36" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U36" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H37" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I37" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J37" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R37" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S37" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T37" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H38" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I38" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S38" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T38" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H39" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I39" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S39" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T39" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U39" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H40" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I40" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J40" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R40" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S40" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T40" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H41" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I41" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S41" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T41" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H42" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I42" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S42" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T42" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U42" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H43" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I43" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J43" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R43" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S43" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T43" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.1087676658888</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H44" t="n">
-        <v>327.2470583971742</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I44" t="n">
-        <v>164.4453669573406</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>74.8684093984361</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S44" t="n">
-        <v>181.8124816465468</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T44" t="n">
-        <v>217.869246549056</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2501353198968</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7046869745314</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H45" t="n">
-        <v>106.0656895195153</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I45" t="n">
-        <v>67.40182153066036</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>60.49432471868085</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S45" t="n">
-        <v>159.8171805378001</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T45" t="n">
-        <v>197.5897947325575</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U45" t="n">
-        <v>225.899353779088</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.455405587967</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H46" t="n">
-        <v>157.4654348025215</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I46" t="n">
-        <v>139.344310992832</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J46" t="n">
-        <v>55.49411454290229</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>41.31504325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R46" t="n">
-        <v>153.2120471148744</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S46" t="n">
-        <v>214.6830078730378</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T46" t="n">
-        <v>225.6572287725438</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2898162417368</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>351452.9027467326</v>
+        <v>349399.0679772008</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>351711.6874722926</v>
+        <v>351428.0744605841</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>345813.8898779048</v>
+        <v>346027.6791870189</v>
       </c>
     </row>
   </sheetData>
@@ -26264,46 +26264,46 @@
         <v>75255.18387201249</v>
       </c>
       <c r="C2" t="n">
-        <v>76408.17196270099</v>
+        <v>75255.18387201249</v>
       </c>
       <c r="D2" t="n">
-        <v>76819.2220506779</v>
+        <v>76373.61126414366</v>
       </c>
       <c r="E2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.8890299865</v>
       </c>
       <c r="F2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="G2" t="n">
-        <v>83145.27143545795</v>
+        <v>82708.8890299865</v>
       </c>
       <c r="H2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.8890299865</v>
       </c>
       <c r="I2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.8890299865</v>
       </c>
       <c r="J2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="K2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="L2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="M2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="N2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="O2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998649</v>
       </c>
       <c r="P2" t="n">
-        <v>83145.27143545794</v>
+        <v>82708.88902998652</v>
       </c>
     </row>
     <row r="3">
@@ -26316,13 +26316,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>21854.448</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10276.968</v>
+        <v>19708.98312032399</v>
       </c>
       <c r="E3" t="n">
-        <v>209688.183</v>
+        <v>205368.4932914853</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>45814.66692941387</v>
       </c>
       <c r="C4" t="n">
-        <v>45820.21489592839</v>
+        <v>45814.66692941387</v>
       </c>
       <c r="D4" t="n">
-        <v>44434.79926958098</v>
+        <v>43499.51359889793</v>
       </c>
       <c r="E4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="F4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="G4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="H4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="I4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="J4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="K4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="L4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="M4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="N4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="O4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
       <c r="P4" t="n">
-        <v>13232.80413607265</v>
+        <v>14387.06177863176</v>
       </c>
     </row>
     <row r="5">
@@ -26420,46 +26420,46 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>34150.8</v>
+        <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>34412.4</v>
+        <v>34129.29174257201</v>
       </c>
       <c r="E5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="F5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="G5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="H5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="I5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="J5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="K5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="L5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="M5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="N5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="O5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="P5" t="n">
-        <v>6474.6</v>
+        <v>6074.278792600922</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6750.748617138379</v>
+        <v>-4187.083057401374</v>
       </c>
       <c r="C6" t="n">
-        <v>-25417.29093322741</v>
+        <v>-4187.083057401374</v>
       </c>
       <c r="D6" t="n">
-        <v>-12304.94521890308</v>
+        <v>-20964.17719765026</v>
       </c>
       <c r="E6" t="n">
-        <v>-146250.3157006147</v>
+        <v>-143120.9448327315</v>
       </c>
       <c r="F6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="G6" t="n">
-        <v>63437.8672993853</v>
+        <v>62247.54845875382</v>
       </c>
       <c r="H6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875382</v>
       </c>
       <c r="I6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875382</v>
       </c>
       <c r="J6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="K6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="L6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="M6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="N6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="O6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875381</v>
       </c>
       <c r="P6" t="n">
-        <v>63437.86729938529</v>
+        <v>62247.54845875384</v>
       </c>
     </row>
   </sheetData>
@@ -26678,46 +26678,46 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="E3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="F3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="G3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="H3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="I3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="J3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="K3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="L3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="M3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="N3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="O3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="P3" t="n">
-        <v>297</v>
+        <v>278.6366418624276</v>
       </c>
     </row>
     <row r="4">
@@ -26895,13 +26895,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>23.01338268678932</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>255.6232591756383</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09648241206030143</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9881005025125623</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3.719638190954774</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8.188824120603016</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12.27292462311558</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15.22564824120603</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>16.94146733668342</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>17.21559798994975</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>16.25620100502513</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>13.87429145728643</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.41901507537688</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6.060663316582915</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.198592964824121</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4223517587939697</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007718592964824113</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05162264150943396</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4985660377358492</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.777358490566038</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.877207547169812</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8.335924528301888</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11.20867924528302</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>13.42618867924528</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12.28233962264151</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>9.857660377358492</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.589584905660378</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.205132075471699</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9588679245283013</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2080754716981131</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003396226415094341</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04327868852459016</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3847868852459019</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.301508196721312</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.059803278688524</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.028196721311474</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6.434360655737706</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6.784131147540982</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.622819672131151</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6.117245901639346</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5.234360655737702</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.624</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.945967213114753</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.754229508196721</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1849180327868852</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00236065573770492</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1447236180904521</v>
+        <v>0.09251611130367558</v>
       </c>
       <c r="H8" t="n">
-        <v>1.482150753768843</v>
+        <v>0.9474806248887679</v>
       </c>
       <c r="I8" t="n">
-        <v>5.579457286432162</v>
+        <v>3.566727381034957</v>
       </c>
       <c r="J8" t="n">
-        <v>12.28323618090452</v>
+        <v>7.852189301760344</v>
       </c>
       <c r="K8" t="n">
-        <v>18.40938693467337</v>
+        <v>11.76839629324494</v>
       </c>
       <c r="L8" t="n">
-        <v>22.83847236180905</v>
+        <v>14.5997362345548</v>
       </c>
       <c r="M8" t="n">
-        <v>25.41220100502512</v>
+        <v>16.24501962895154</v>
       </c>
       <c r="N8" t="n">
-        <v>25.82339698492462</v>
+        <v>16.50788103019311</v>
       </c>
       <c r="O8" t="n">
-        <v>24.38430150753769</v>
+        <v>15.58792394841718</v>
       </c>
       <c r="P8" t="n">
-        <v>20.81143718592965</v>
+        <v>13.30393245060769</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.62852261306532</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>9.090994974874373</v>
+        <v>5.811515176679516</v>
       </c>
       <c r="S8" t="n">
-        <v>3.297889447236182</v>
+        <v>2.108210886332509</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6335276381909546</v>
+        <v>0.4049892772318401</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01157788944723617</v>
+        <v>0.007401288904294046</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07743396226415095</v>
+        <v>0.0495004835149808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7478490566037738</v>
+        <v>0.4780704592104726</v>
       </c>
       <c r="I9" t="n">
-        <v>2.666037735849057</v>
+        <v>1.704292963125436</v>
       </c>
       <c r="J9" t="n">
-        <v>7.315811320754718</v>
+        <v>4.676710155246499</v>
       </c>
       <c r="K9" t="n">
-        <v>12.50388679245283</v>
+        <v>7.993242550750212</v>
       </c>
       <c r="L9" t="n">
-        <v>16.81301886792453</v>
+        <v>10.74790103688213</v>
       </c>
       <c r="M9" t="n">
-        <v>19.62</v>
+        <v>12.54229356430018</v>
       </c>
       <c r="N9" t="n">
-        <v>20.13928301886792</v>
+        <v>12.87425075418792</v>
       </c>
       <c r="O9" t="n">
-        <v>18.42350943396226</v>
+        <v>11.77742425104019</v>
       </c>
       <c r="P9" t="n">
-        <v>14.78649056603774</v>
+        <v>9.452421277522957</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.884377358490568</v>
+        <v>6.318693299210532</v>
       </c>
       <c r="R9" t="n">
-        <v>4.807698113207549</v>
+        <v>3.073372125605564</v>
       </c>
       <c r="S9" t="n">
-        <v>1.438301886792452</v>
+        <v>0.9194497705523841</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3121132075471697</v>
+        <v>0.1995216857467866</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005094339622641512</v>
+        <v>0.003256610757564528</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06491803278688524</v>
+        <v>0.04149954254994795</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5771803278688528</v>
+        <v>0.3689686601259011</v>
       </c>
       <c r="I10" t="n">
-        <v>1.952262295081968</v>
+        <v>1.248004425047526</v>
       </c>
       <c r="J10" t="n">
-        <v>4.589704918032786</v>
+        <v>2.93401765828132</v>
       </c>
       <c r="K10" t="n">
-        <v>7.542295081967211</v>
+        <v>4.821492307166679</v>
       </c>
       <c r="L10" t="n">
-        <v>9.651540983606559</v>
+        <v>6.169850171471354</v>
       </c>
       <c r="M10" t="n">
-        <v>10.17619672131147</v>
+        <v>6.505241928988658</v>
       </c>
       <c r="N10" t="n">
-        <v>9.934229508196728</v>
+        <v>6.350561815847949</v>
       </c>
       <c r="O10" t="n">
-        <v>9.175868852459018</v>
+        <v>5.865771705150827</v>
       </c>
       <c r="P10" t="n">
-        <v>7.851540983606554</v>
+        <v>5.019181037131885</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.436</v>
+        <v>3.475020785705187</v>
       </c>
       <c r="R10" t="n">
-        <v>2.91895081967213</v>
+        <v>1.865970340473114</v>
       </c>
       <c r="S10" t="n">
-        <v>1.131344262295082</v>
+        <v>0.7232238460750018</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2773770491803278</v>
+        <v>0.1773162272588684</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003540983606557381</v>
+        <v>0.002263611411815345</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H11" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I11" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J11" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K11" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L11" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M11" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N11" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O11" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P11" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q11" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R11" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S11" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T11" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H12" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I12" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J12" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K12" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q12" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R12" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S12" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T12" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H13" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I13" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J13" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K13" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L13" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M13" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N13" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O13" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P13" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R13" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S13" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T13" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H14" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I14" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J14" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028629</v>
       </c>
       <c r="K14" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L14" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M14" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N14" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O14" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P14" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q14" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R14" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S14" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T14" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H15" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557224</v>
       </c>
       <c r="I15" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J15" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K15" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q15" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R15" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S15" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T15" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109827</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125744</v>
       </c>
       <c r="H16" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I16" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J16" t="n">
-        <v>37.86506557377049</v>
+        <v>35.523887930559</v>
       </c>
       <c r="K16" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L16" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M16" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N16" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O16" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P16" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.847</v>
+        <v>42.07413292122656</v>
       </c>
       <c r="R16" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S16" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T16" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H17" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I17" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J17" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K17" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L17" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M17" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N17" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O17" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P17" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q17" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R17" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S17" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T17" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H18" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I18" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J18" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K18" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q18" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R18" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S18" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T18" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H19" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I19" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J19" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K19" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L19" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M19" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N19" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O19" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P19" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R19" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S19" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T19" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H20" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I20" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J20" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K20" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L20" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M20" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N20" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O20" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P20" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q20" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R20" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S20" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T20" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H21" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I21" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J21" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K21" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q21" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R21" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S21" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T21" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H22" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I22" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J22" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K22" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L22" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M22" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N22" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O22" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P22" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R22" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S22" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T22" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H23" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I23" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J23" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K23" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L23" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M23" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N23" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O23" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P23" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q23" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R23" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S23" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T23" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H24" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I24" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J24" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K24" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q24" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R24" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S24" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T24" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H25" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I25" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J25" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K25" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L25" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M25" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N25" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O25" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P25" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R25" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S25" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T25" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H26" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I26" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J26" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K26" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L26" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M26" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N26" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O26" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P26" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q26" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R26" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S26" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T26" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H27" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I27" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J27" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K27" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q27" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R27" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S27" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T27" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H28" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I28" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J28" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K28" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L28" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M28" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N28" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O28" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P28" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R28" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S28" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T28" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H29" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I29" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J29" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K29" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L29" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M29" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N29" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O29" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P29" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q29" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R29" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S29" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T29" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H30" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I30" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J30" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K30" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q30" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R30" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S30" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H31" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I31" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J31" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K31" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L31" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M31" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N31" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O31" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P31" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q31" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R31" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S31" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T31" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H32" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I32" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J32" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K32" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L32" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M32" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N32" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O32" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P32" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q32" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R32" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S32" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T32" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H33" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I33" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J33" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K33" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q33" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R33" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S33" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T33" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H34" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I34" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J34" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K34" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L34" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M34" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N34" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O34" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P34" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R34" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S34" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T34" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H35" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I35" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J35" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K35" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L35" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M35" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N35" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O35" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P35" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q35" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R35" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S35" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T35" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H36" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I36" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J36" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K36" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q36" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R36" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S36" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T36" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H37" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I37" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J37" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K37" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L37" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M37" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N37" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O37" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P37" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q37" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R37" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S37" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T37" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H38" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I38" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J38" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K38" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L38" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M38" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N38" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O38" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P38" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q38" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R38" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S38" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T38" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U38" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H39" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I39" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J39" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K39" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q39" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R39" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S39" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T39" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H40" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I40" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J40" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K40" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L40" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M40" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N40" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O40" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P40" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R40" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S40" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T40" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H41" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I41" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J41" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K41" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L41" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M41" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N41" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O41" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P41" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q41" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R41" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S41" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T41" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H42" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I42" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J42" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K42" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q42" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R42" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S42" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T42" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H43" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I43" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J43" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K43" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L43" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M43" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N43" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O43" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P43" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R43" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S43" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T43" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.19396984924623</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H44" t="n">
-        <v>12.22774371859296</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I44" t="n">
-        <v>46.03052261306534</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J44" t="n">
-        <v>101.3366984924623</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K44" t="n">
-        <v>151.8774422110553</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L44" t="n">
-        <v>188.4173969849246</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M44" t="n">
-        <v>209.6506582914573</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N44" t="n">
-        <v>213.0430251256282</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O44" t="n">
-        <v>201.1704874371859</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P44" t="n">
-        <v>171.6943567839196</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q44" t="n">
-        <v>128.9353115577889</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R44" t="n">
-        <v>75.00070854271358</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S44" t="n">
-        <v>27.2075879396985</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T44" t="n">
-        <v>5.226603015075376</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0955175879396984</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6388301886792453</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H45" t="n">
-        <v>6.169754716981133</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I45" t="n">
-        <v>21.99481132075472</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J45" t="n">
-        <v>60.35544339622643</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K45" t="n">
-        <v>103.1570660377359</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>121.9885471698113</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q45" t="n">
-        <v>81.54611320754718</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R45" t="n">
-        <v>39.66350943396228</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S45" t="n">
-        <v>11.86599056603773</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T45" t="n">
-        <v>2.57493396226415</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04202830188679247</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5355737704918032</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H46" t="n">
-        <v>4.761737704918036</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I46" t="n">
-        <v>16.10616393442623</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J46" t="n">
-        <v>37.86506557377049</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K46" t="n">
-        <v>62.22393442622949</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L46" t="n">
-        <v>79.6252131147541</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M46" t="n">
-        <v>83.95362295081965</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N46" t="n">
-        <v>81.957393442623</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O46" t="n">
-        <v>75.7009180327869</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P46" t="n">
-        <v>64.77521311475407</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.847</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R46" t="n">
-        <v>24.08134426229507</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S46" t="n">
-        <v>9.333590163934423</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T46" t="n">
-        <v>2.288360655737704</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02921311475409839</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
